--- a/data/trans_camb/P16A09-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A09-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,73; -0,63</t>
+          <t>-4,71; -0,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,96; -1,17</t>
+          <t>-5,11; -1,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 0,36</t>
+          <t>-4,26; -0,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 4,75</t>
+          <t>0,02; 5,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 1,72</t>
+          <t>-3,19; 1,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 5,85</t>
+          <t>0,26; 5,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 2,0</t>
+          <t>-1,34; 1,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,37; -0,31</t>
+          <t>-3,3; 0,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,94</t>
+          <t>-0,81; 2,68</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-61,34; -11,05</t>
+          <t>-61,56; -13,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-65,09; -20,64</t>
+          <t>-66,83; -19,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-54,39; 6,61</t>
+          <t>-54,97; 2,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 54,39</t>
+          <t>-0,36; 54,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,74; 19,87</t>
+          <t>-28,83; 18,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 62,33</t>
+          <t>1,34; 61,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 25,55</t>
+          <t>-14,54; 24,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,41; -3,73</t>
+          <t>-36,1; 1,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 38,67</t>
+          <t>-8,74; 33,18</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,81</t>
+          <t>-0,64; 0,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,27</t>
+          <t>-1,08; 0,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,04</t>
+          <t>-0,51; 1,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,05</t>
+          <t>-0,82; 1,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,19</t>
+          <t>-0,68; 1,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,25</t>
+          <t>0,27; 2,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 0,74</t>
+          <t>-0,53; 0,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,42</t>
+          <t>-0,69; 0,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,43</t>
+          <t>0,13; 1,48</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-42,87; 94,06</t>
+          <t>-41,86; 114,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-65,2; 38,23</t>
+          <t>-66,62; 38,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-33,22; 122,53</t>
+          <t>-30,34; 135,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-36,34; 87,32</t>
+          <t>-37,98; 83,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,8; 102,6</t>
+          <t>-31,95; 96,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,08; 175,91</t>
+          <t>11,28; 186,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,87; 63,85</t>
+          <t>-29,65; 61,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-39,03; 39,4</t>
+          <t>-39,66; 45,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,42; 119,43</t>
+          <t>6,28; 129,42</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 2,44</t>
+          <t>-1,21; 2,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,04; -0,44</t>
+          <t>-2,67; -0,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,58; -0,16</t>
+          <t>-2,55; -0,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 0,81</t>
+          <t>-2,75; 0,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,62; -0,21</t>
+          <t>-3,55; -0,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 2,18</t>
+          <t>-1,26; 2,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,9</t>
+          <t>-1,6; 1,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,48; -0,5</t>
+          <t>-2,42; -0,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,83</t>
+          <t>-1,22; 0,76</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-78,19; 463,12</t>
+          <t>-80,15; 502,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 40,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-83,51; 79,9</t>
+          <t>-83,3; 64,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-92,89; 16,75</t>
+          <t>-94,04; 1,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-42,0; 167,45</t>
+          <t>-37,8; 185,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-70,86; 90,54</t>
+          <t>-66,29; 93,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-94,75; -35,54</t>
+          <t>-95,63; -32,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-51,04; 76,78</t>
+          <t>-51,16; 78,54</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,04</t>
+          <t>-1,57; -0,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,4; -0,92</t>
+          <t>-2,28; -0,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,99; -0,41</t>
+          <t>-1,92; -0,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 1,84</t>
+          <t>-0,34; 1,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,29; -0,24</t>
+          <t>-2,36; -0,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,97</t>
+          <t>-1,17; 1,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,67</t>
+          <t>-0,74; 0,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,04; -0,79</t>
+          <t>-2,06; -0,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,07</t>
+          <t>-1,25; 0,17</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-50,25; 1,77</t>
+          <t>-48,95; -1,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-69,49; -35,15</t>
+          <t>-67,71; -35,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-57,92; -17,34</t>
+          <t>-58,68; -18,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 40,54</t>
+          <t>-5,95; 41,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-40,11; -4,83</t>
+          <t>-41,61; -5,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-20,36; 21,16</t>
+          <t>-21,04; 23,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-15,55; 18,0</t>
+          <t>-16,84; 16,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-46,64; -21,53</t>
+          <t>-47,25; -22,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-29,06; 1,87</t>
+          <t>-27,89; 5,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A09-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A09-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-2,0</t>
+          <t>-2,24</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,74</t>
+          <t>2,31</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>0,53</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,71; -0,96</t>
+          <t>-4,64; -0,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,11; -1,13</t>
+          <t>-4,89; -0,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,26; -0,03</t>
+          <t>-4,24; -0,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 5,01</t>
+          <t>0,08; 4,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 1,66</t>
+          <t>-3,61; 1,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 5,69</t>
+          <t>-0,08; 4,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,96</t>
+          <t>-1,43; 2,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 0,1</t>
+          <t>-3,34; -0,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 2,68</t>
+          <t>-1,31; 2,32</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-30,13%</t>
+          <t>-33,73%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-61,56; -13,71</t>
+          <t>-60,15; -9,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-66,83; -19,65</t>
+          <t>-65,18; -15,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-54,97; 2,12</t>
+          <t>-56,09; -2,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 54,5</t>
+          <t>0,24; 53,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,83; 18,58</t>
+          <t>-32,37; 19,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 61,69</t>
+          <t>-0,73; 51,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,54; 24,9</t>
+          <t>-14,93; 26,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,1; 1,17</t>
+          <t>-35,14; -0,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 33,18</t>
+          <t>-13,12; 30,02</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,36</t>
+          <t>1,83</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>1,19</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,91</t>
+          <t>-0,68; 0,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,3</t>
+          <t>-1,06; 0,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,16</t>
+          <t>-0,3; 1,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,06</t>
+          <t>-0,82; 1,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,13</t>
+          <t>-0,75; 1,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,36</t>
+          <t>0,99; 2,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,69</t>
+          <t>-0,47; 0,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,51</t>
+          <t>-0,63; 0,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,48</t>
+          <t>0,58; 1,72</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>108,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>82,42%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-41,86; 114,83</t>
+          <t>-44,48; 96,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-66,62; 38,78</t>
+          <t>-66,14; 38,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-30,34; 135,85</t>
+          <t>-19,38; 153,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,98; 83,51</t>
+          <t>-38,31; 89,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,95; 96,05</t>
+          <t>-34,57; 103,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,28; 186,01</t>
+          <t>41,76; 228,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,65; 61,02</t>
+          <t>-27,54; 69,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-39,66; 45,28</t>
+          <t>-36,8; 43,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,28; 129,42</t>
+          <t>32,42; 155,9</t>
         </is>
       </c>
     </row>
@@ -1066,14 +1066,14 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>-0,98</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-0,95</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,95</t>
-        </is>
-      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-1,61</t>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,8</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>-0,02</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,24</t>
+          <t>-1,14; 2,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,67; -0,41</t>
+          <t>-2,52; -0,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; -0,12</t>
+          <t>-2,54; -0,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 0,7</t>
+          <t>-3,1; 0,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,55; -0,19</t>
+          <t>-3,58; -0,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,25</t>
+          <t>-1,22; 2,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,01</t>
+          <t>-1,45; 1,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,42; -0,49</t>
+          <t>-2,43; -0,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,76</t>
+          <t>-1,17; 1,03</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-81,6%</t>
+          <t>-84,26%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-7,79%</t>
+          <t>-1,41%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-80,15; 502,14</t>
+          <t>-74,22; 515,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 38,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-83,3; 64,38</t>
+          <t>-82,55; 74,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-94,04; 1,75</t>
+          <t>-92,49; 11,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-37,8; 185,13</t>
+          <t>-34,49; 187,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-66,29; 93,91</t>
+          <t>-64,57; 111,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-95,63; -32,75</t>
+          <t>-93,79; -27,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-51,16; 78,54</t>
+          <t>-46,61; 103,38</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,15</t>
+          <t>-1,04</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,02</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>-0,31</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,57; -0,06</t>
+          <t>-1,63; 0,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,28; -0,91</t>
+          <t>-2,33; -0,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,92; -0,49</t>
+          <t>-1,85; -0,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,85</t>
+          <t>-0,38; 1,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,36; -0,24</t>
+          <t>-2,27; -0,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,1</t>
+          <t>-0,65; 1,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,64</t>
+          <t>-0,71; 0,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,06; -0,84</t>
+          <t>-2,07; -0,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,17</t>
+          <t>-0,91; 0,33</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-39,61%</t>
+          <t>-35,72%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-0,39%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-13,88%</t>
+          <t>-7,84%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-48,95; -1,59</t>
+          <t>-48,62; 2,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-67,71; -35,0</t>
+          <t>-69,61; -35,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-58,68; -18,87</t>
+          <t>-53,97; -13,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 41,84</t>
+          <t>-7,43; 41,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-41,61; -5,2</t>
+          <t>-39,89; -5,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 23,99</t>
+          <t>-11,63; 29,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 16,9</t>
+          <t>-16,11; 16,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-47,25; -22,44</t>
+          <t>-47,35; -21,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-27,89; 5,3</t>
+          <t>-20,69; 8,93</t>
         </is>
       </c>
     </row>
